--- a/data/trans_orig/P1403-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1403-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipertensión en 2007</t>
+          <t>Población con diagnóstico de hipertensión en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90689</t>
+          <t>90821</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>127265</t>
+          <t>129989</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91373</t>
+          <t>91176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>129784</t>
+          <t>130024</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>193289</t>
+          <t>190327</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>246286</t>
+          <t>245365</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>566747</t>
+          <t>564023</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>603323</t>
+          <t>603191</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>558567</t>
+          <t>558327</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>596978</t>
+          <t>597175</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1136077</t>
+          <t>1136998</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1189074</t>
+          <t>1192036</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,23%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96977</t>
+          <t>97246</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>138764</t>
+          <t>134453</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>154042</t>
+          <t>154833</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>202084</t>
+          <t>204893</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>263662</t>
+          <t>260916</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>327334</t>
+          <t>325235</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>823036</t>
+          <t>827347</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>864823</t>
+          <t>864554</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>766309</t>
+          <t>763500</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>814351</t>
+          <t>813560</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1602859</t>
+          <t>1604958</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1666531</t>
+          <t>1669277</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,48%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69996</t>
+          <t>67338</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>103450</t>
+          <t>104372</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99644</t>
+          <t>100157</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>139177</t>
+          <t>139224</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>180761</t>
+          <t>179391</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>233775</t>
+          <t>230752</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>575059</t>
+          <t>574137</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>608513</t>
+          <t>611171</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>544664</t>
+          <t>544617</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>584197</t>
+          <t>583684</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1128575</t>
+          <t>1131598</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1181589</t>
+          <t>1182959</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,83%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>99799</t>
+          <t>98477</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>135765</t>
+          <t>136319</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>145911</t>
+          <t>146026</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>194444</t>
+          <t>193267</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>255625</t>
+          <t>255062</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>312375</t>
+          <t>315618</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>806457</t>
+          <t>805903</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>842423</t>
+          <t>843745</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>844168</t>
+          <t>845345</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>892701</t>
+          <t>892586</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1668459</t>
+          <t>1665216</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1725209</t>
+          <t>1725772</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,12%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>388336</t>
+          <t>391893</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>465680</t>
+          <t>469366</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>528587</t>
+          <t>533039</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>619019</t>
+          <t>616523</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>945675</t>
+          <t>948521</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1060345</t>
+          <t>1059189</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2810863</t>
+          <t>2807177</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2888207</t>
+          <t>2884650</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2760178</t>
+          <t>2762674</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2850610</t>
+          <t>2846158</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5595396</t>
+          <t>5596552</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5710066</t>
+          <t>5707220</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipertensión en 2012</t>
+          <t>Población con diagnóstico de hipertensión en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>117977</t>
+          <t>115681</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>161546</t>
+          <t>158461</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>148363</t>
+          <t>148358</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>195029</t>
+          <t>191308</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>277716</t>
+          <t>277843</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>338986</t>
+          <t>340831</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,34%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>541923</t>
+          <t>545008</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>585492</t>
+          <t>587788</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>502021</t>
+          <t>505742</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>548687</t>
+          <t>548692</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1061533</t>
+          <t>1059688</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1122803</t>
+          <t>1122676</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,16%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125179</t>
+          <t>125129</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>172885</t>
+          <t>174276</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>166919</t>
+          <t>168817</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>220773</t>
+          <t>220576</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>310771</t>
+          <t>309605</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>379850</t>
+          <t>376667</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>845062</t>
+          <t>843671</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>892768</t>
+          <t>892818</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>808200</t>
+          <t>808397</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>862054</t>
+          <t>860156</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1667071</t>
+          <t>1670254</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1736150</t>
+          <t>1737316</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94202</t>
+          <t>91525</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>136921</t>
+          <t>134184</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>112974</t>
+          <t>113216</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157114</t>
+          <t>159016</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>219111</t>
+          <t>216816</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>278323</t>
+          <t>279626</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>620702</t>
+          <t>623439</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663421</t>
+          <t>666098</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>618951</t>
+          <t>617049</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>663091</t>
+          <t>662849</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1255366</t>
+          <t>1254063</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1314578</t>
+          <t>1316873</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,86%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>153501</t>
+          <t>154195</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>203434</t>
+          <t>204352</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>218060</t>
+          <t>218003</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>276577</t>
+          <t>275292</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>384648</t>
+          <t>385993</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>462912</t>
+          <t>464565</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>744305</t>
+          <t>743387</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>794238</t>
+          <t>793544</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>775324</t>
+          <t>776609</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>833841</t>
+          <t>833898</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1536728</t>
+          <t>1535075</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1614992</t>
+          <t>1613647</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,7%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>529684</t>
+          <t>529427</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>631117</t>
+          <t>618780</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>695616</t>
+          <t>691577</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>796065</t>
+          <t>792112</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1249465</t>
+          <t>1257558</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1387466</t>
+          <t>1382834</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2795662</t>
+          <t>2807999</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2897095</t>
+          <t>2897352</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2757925</t>
+          <t>2761878</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2858374</t>
+          <t>2862413</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5593303</t>
+          <t>5597935</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5731304</t>
+          <t>5723211</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipertensión en 2016</t>
+          <t>Población con diagnóstico de hipertensión en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85060</t>
+          <t>85976</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>122421</t>
+          <t>122953</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>113839</t>
+          <t>112554</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>154250</t>
+          <t>153156</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>208056</t>
+          <t>208587</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>261508</t>
+          <t>265202</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>552379</t>
+          <t>551847</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>589740</t>
+          <t>588824</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>518589</t>
+          <t>519683</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>559000</t>
+          <t>560285</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1086131</t>
+          <t>1082437</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1139583</t>
+          <t>1139052</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>135230</t>
+          <t>136234</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>181765</t>
+          <t>180757</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>153153</t>
+          <t>153380</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>206323</t>
+          <t>203533</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>300366</t>
+          <t>297665</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>375226</t>
+          <t>373446</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>840666</t>
+          <t>841674</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>887201</t>
+          <t>886197</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>836590</t>
+          <t>839380</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>889760</t>
+          <t>889533</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1690118</t>
+          <t>1691898</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1764978</t>
+          <t>1767679</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,59%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90546</t>
+          <t>89157</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130182</t>
+          <t>129733</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>118152</t>
+          <t>119298</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>166228</t>
+          <t>166923</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>223846</t>
+          <t>220436</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>283431</t>
+          <t>284571</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>629370</t>
+          <t>629819</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>669006</t>
+          <t>670395</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>618783</t>
+          <t>618088</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>666859</t>
+          <t>665713</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1261132</t>
+          <t>1259992</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1320717</t>
+          <t>1324127</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,73%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>123440</t>
+          <t>124393</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>166419</t>
+          <t>167286</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>156574</t>
+          <t>156015</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>208426</t>
+          <t>208771</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>291325</t>
+          <t>292571</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>364677</t>
+          <t>357947</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>771148</t>
+          <t>770281</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>814127</t>
+          <t>813174</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>835353</t>
+          <t>835008</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>887205</t>
+          <t>887764</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1616669</t>
+          <t>1623399</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1690021</t>
+          <t>1688775</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,23%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>475498</t>
+          <t>473573</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>556729</t>
+          <t>555243</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>583550</t>
+          <t>582971</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>682867</t>
+          <t>676205</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1081724</t>
+          <t>1077061</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1206179</t>
+          <t>1201718</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2837621</t>
+          <t>2839107</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2918852</t>
+          <t>2920777</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2861675</t>
+          <t>2868337</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2960992</t>
+          <t>2961571</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5732713</t>
+          <t>5737174</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5857168</t>
+          <t>5861831</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,48%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipertensión en 2023</t>
+          <t>Población con diagnóstico de hipertensión en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>119345</t>
+          <t>118620</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>158566</t>
+          <t>156624</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>154670</t>
+          <t>154012</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>187163</t>
+          <t>185457</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>280339</t>
+          <t>282484</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>329902</t>
+          <t>332088</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>476326</t>
+          <t>478268</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>515547</t>
+          <t>516272</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>488207</t>
+          <t>489913</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>520700</t>
+          <t>521358</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>980360</t>
+          <t>978174</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1029923</t>
+          <t>1027778</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92787</t>
+          <t>73806</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>218369</t>
+          <t>217610</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>166508</t>
+          <t>168640</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>203088</t>
+          <t>203695</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>227427</t>
+          <t>222849</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>404950</t>
+          <t>404012</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>973687</t>
+          <t>974446</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1099269</t>
+          <t>1118250</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>753822</t>
+          <t>753215</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>790402</t>
+          <t>788270</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1744017</t>
+          <t>1744955</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1921540</t>
+          <t>1926118</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,63%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115841</t>
+          <t>116978</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>157511</t>
+          <t>159476</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>142719</t>
+          <t>142115</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>616771</t>
+          <t>617605</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>277368</t>
+          <t>279732</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>884588</t>
+          <t>925513</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>56,61%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>545291</t>
+          <t>543326</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>586961</t>
+          <t>585824</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>315248</t>
+          <t>314414</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>789300</t>
+          <t>789904</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>750233</t>
+          <t>709308</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1357453</t>
+          <t>1355089</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,89%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>160772</t>
+          <t>160886</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>205025</t>
+          <t>205770</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>196282</t>
+          <t>195820</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>271529</t>
+          <t>273792</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>377316</t>
+          <t>377911</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>461123</t>
+          <t>460379</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>720790</t>
+          <t>720045</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>765043</t>
+          <t>764929</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>819368</t>
+          <t>817105</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>894615</t>
+          <t>895077</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1555588</t>
+          <t>1556332</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1639395</t>
+          <t>1638800</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,26%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>491642</t>
+          <t>483909</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>687285</t>
+          <t>689114</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>748005</t>
+          <t>742025</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1482576</t>
+          <t>1477015</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1339617</t>
+          <t>1335900</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2252052</t>
+          <t>2124866</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2768280</t>
+          <t>2766451</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2963923</t>
+          <t>2971656</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2172620</t>
+          <t>2178181</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2907191</t>
+          <t>2913171</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4858709</t>
+          <t>4985895</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5771144</t>
+          <t>5774861</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1403-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1403-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90821</t>
+          <t>90152</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129989</t>
+          <t>129110</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91176</t>
+          <t>93954</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>130024</t>
+          <t>129727</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>190327</t>
+          <t>193275</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>245365</t>
+          <t>247237</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>564023</t>
+          <t>564902</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>603191</t>
+          <t>603860</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>558327</t>
+          <t>558624</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>597175</t>
+          <t>594397</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1136998</t>
+          <t>1135126</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1192036</t>
+          <t>1189088</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,02%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>97246</t>
+          <t>97675</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>134453</t>
+          <t>138170</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>154833</t>
+          <t>152290</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>204893</t>
+          <t>202883</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>260916</t>
+          <t>260356</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>325235</t>
+          <t>325932</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>827347</t>
+          <t>823630</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>864554</t>
+          <t>864125</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>763500</t>
+          <t>765510</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>813560</t>
+          <t>816103</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1604958</t>
+          <t>1604261</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1669277</t>
+          <t>1669837</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,51%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67338</t>
+          <t>70608</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104372</t>
+          <t>105046</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100157</t>
+          <t>99372</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>139224</t>
+          <t>137223</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>179391</t>
+          <t>182205</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>230752</t>
+          <t>233573</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>574137</t>
+          <t>573463</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>611171</t>
+          <t>607901</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>544617</t>
+          <t>546618</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>583684</t>
+          <t>584469</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1131598</t>
+          <t>1128777</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1182959</t>
+          <t>1180145</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,63%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98477</t>
+          <t>98935</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>136319</t>
+          <t>135643</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>146026</t>
+          <t>144815</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>193267</t>
+          <t>190769</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>255062</t>
+          <t>254394</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>315618</t>
+          <t>315277</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>805903</t>
+          <t>806579</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>843745</t>
+          <t>843287</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>845345</t>
+          <t>847843</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>892586</t>
+          <t>893797</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1665216</t>
+          <t>1665557</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1725772</t>
+          <t>1726440</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>391893</t>
+          <t>390835</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>469366</t>
+          <t>467759</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>533039</t>
+          <t>533685</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>616523</t>
+          <t>618416</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>948521</t>
+          <t>934256</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1059189</t>
+          <t>1053357</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2807177</t>
+          <t>2808784</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2884650</t>
+          <t>2885708</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2762674</t>
+          <t>2760781</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2846158</t>
+          <t>2845512</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5596552</t>
+          <t>5602384</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5707220</t>
+          <t>5721485</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>115681</t>
+          <t>115554</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>158461</t>
+          <t>159406</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>148358</t>
+          <t>148321</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>191308</t>
+          <t>196294</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>277843</t>
+          <t>278067</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>340831</t>
+          <t>342575</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>545008</t>
+          <t>544063</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>587788</t>
+          <t>587915</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>505742</t>
+          <t>500756</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>548692</t>
+          <t>548729</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1059688</t>
+          <t>1057944</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1122676</t>
+          <t>1122452</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,15%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125129</t>
+          <t>127862</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>174276</t>
+          <t>175155</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>168817</t>
+          <t>165759</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>220576</t>
+          <t>219195</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>309605</t>
+          <t>308024</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>376667</t>
+          <t>376286</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>843671</t>
+          <t>842792</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>892818</t>
+          <t>890085</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>808397</t>
+          <t>809778</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>860156</t>
+          <t>863214</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1670254</t>
+          <t>1670635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1737316</t>
+          <t>1738897</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,95%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91525</t>
+          <t>93345</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134184</t>
+          <t>136041</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>113216</t>
+          <t>111563</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>159016</t>
+          <t>157173</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>216816</t>
+          <t>219392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>279626</t>
+          <t>278133</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>623439</t>
+          <t>621582</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>666098</t>
+          <t>664278</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>617049</t>
+          <t>618892</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>662849</t>
+          <t>664502</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1254063</t>
+          <t>1255556</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1316873</t>
+          <t>1314297</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,7%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>154195</t>
+          <t>154426</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>204352</t>
+          <t>206711</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>218003</t>
+          <t>218816</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>275292</t>
+          <t>274088</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>385993</t>
+          <t>385084</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>464565</t>
+          <t>462146</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>743387</t>
+          <t>741028</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>793544</t>
+          <t>793313</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>776609</t>
+          <t>777813</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>833898</t>
+          <t>833085</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1535075</t>
+          <t>1537494</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1613647</t>
+          <t>1614556</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,74%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>529427</t>
+          <t>531292</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>618780</t>
+          <t>625083</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>691577</t>
+          <t>695173</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>792112</t>
+          <t>796731</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1257558</t>
+          <t>1256085</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1382834</t>
+          <t>1389061</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2807999</t>
+          <t>2801696</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2897352</t>
+          <t>2895487</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2761878</t>
+          <t>2757259</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2862413</t>
+          <t>2858817</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5597935</t>
+          <t>5591708</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5723211</t>
+          <t>5724684</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,01%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85976</t>
+          <t>87117</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>122953</t>
+          <t>121412</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>112554</t>
+          <t>110630</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>153156</t>
+          <t>153039</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>208587</t>
+          <t>206996</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>265202</t>
+          <t>261707</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>551847</t>
+          <t>553388</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>588824</t>
+          <t>587683</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>519683</t>
+          <t>519800</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>560285</t>
+          <t>562209</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1082437</t>
+          <t>1085932</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1139052</t>
+          <t>1140643</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,64%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>136234</t>
+          <t>138139</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>180757</t>
+          <t>185711</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>153380</t>
+          <t>150757</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>203533</t>
+          <t>200384</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>297665</t>
+          <t>302106</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>373446</t>
+          <t>370831</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>841674</t>
+          <t>836720</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>886197</t>
+          <t>884292</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>839380</t>
+          <t>842529</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>889533</t>
+          <t>892156</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1691898</t>
+          <t>1694513</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1767679</t>
+          <t>1763238</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,37%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89157</t>
+          <t>88647</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129733</t>
+          <t>129804</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119298</t>
+          <t>118073</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>166923</t>
+          <t>165350</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>220436</t>
+          <t>219220</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>284571</t>
+          <t>281725</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>629819</t>
+          <t>629748</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>670395</t>
+          <t>670905</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>618088</t>
+          <t>619661</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>665713</t>
+          <t>666938</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1259992</t>
+          <t>1262838</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1324127</t>
+          <t>1325343</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,81%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>124393</t>
+          <t>123951</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>167286</t>
+          <t>166233</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>156015</t>
+          <t>155344</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>208771</t>
+          <t>207088</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>292571</t>
+          <t>291810</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>357947</t>
+          <t>362039</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>770281</t>
+          <t>771334</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>813174</t>
+          <t>813616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>835008</t>
+          <t>836691</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>887764</t>
+          <t>888435</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1623399</t>
+          <t>1619307</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1688775</t>
+          <t>1689536</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>473573</t>
+          <t>469734</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>555243</t>
+          <t>553028</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>582971</t>
+          <t>583146</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>676205</t>
+          <t>679166</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1077061</t>
+          <t>1083303</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1201718</t>
+          <t>1215326</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2839107</t>
+          <t>2841322</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2920777</t>
+          <t>2924616</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2868337</t>
+          <t>2865376</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2961571</t>
+          <t>2961396</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5737174</t>
+          <t>5723566</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5861831</t>
+          <t>5855589</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>136593</t>
+          <t>146841</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>118620</t>
+          <t>127545</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>156624</t>
+          <t>168015</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>170007</t>
+          <t>180848</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>154012</t>
+          <t>164523</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>185457</t>
+          <t>197411</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>306600</t>
+          <t>327688</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>282484</t>
+          <t>301597</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>332088</t>
+          <t>355372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>498299</t>
+          <t>543309</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>478268</t>
+          <t>522135</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>516272</t>
+          <t>562605</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>505363</t>
+          <t>551874</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>489913</t>
+          <t>535311</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>521358</t>
+          <t>568199</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1003662</t>
+          <t>1095183</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>978174</t>
+          <t>1067499</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1027778</t>
+          <t>1121274</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,8%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634892</t>
+          <t>690150</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634892</t>
+          <t>690150</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634892</t>
+          <t>690150</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310262</t>
+          <t>1422871</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310262</t>
+          <t>1422871</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310262</t>
+          <t>1422871</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>165963</t>
+          <t>182309</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73806</t>
+          <t>160545</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>217610</t>
+          <t>206170</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>184738</t>
+          <t>204022</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>168640</t>
+          <t>184142</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>203695</t>
+          <t>224823</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>350702</t>
+          <t>386331</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>222849</t>
+          <t>353851</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>404012</t>
+          <t>421317</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1026093</t>
+          <t>865604</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>974446</t>
+          <t>841743</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1118250</t>
+          <t>887368</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>772172</t>
+          <t>865596</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>753215</t>
+          <t>844795</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>788270</t>
+          <t>885476</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1798265</t>
+          <t>1731200</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1744955</t>
+          <t>1696214</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1926118</t>
+          <t>1763680</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>83,29%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192056</t>
+          <t>1047913</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192056</t>
+          <t>1047913</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192056</t>
+          <t>1047913</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>956910</t>
+          <t>1069618</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>956910</t>
+          <t>1069618</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>956910</t>
+          <t>1069618</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2148967</t>
+          <t>2117531</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2148967</t>
+          <t>2117531</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2148967</t>
+          <t>2117531</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>136687</t>
+          <t>158230</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>116978</t>
+          <t>136544</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>159476</t>
+          <t>182830</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>321640</t>
+          <t>136565</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>142115</t>
+          <t>119357</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>617605</t>
+          <t>154688</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>458327</t>
+          <t>294794</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>279732</t>
+          <t>269866</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>925513</t>
+          <t>326214</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>566115</t>
+          <t>641621</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>543326</t>
+          <t>617021</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>585824</t>
+          <t>663307</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>610379</t>
+          <t>673797</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314414</t>
+          <t>655674</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>789904</t>
+          <t>691005</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1176494</t>
+          <t>1315418</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>709308</t>
+          <t>1283998</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1355089</t>
+          <t>1340346</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,24%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>702802</t>
+          <t>799851</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>702802</t>
+          <t>799851</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>702802</t>
+          <t>799851</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932019</t>
+          <t>810362</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932019</t>
+          <t>810362</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932019</t>
+          <t>810362</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1634821</t>
+          <t>1610212</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1634821</t>
+          <t>1610212</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1634821</t>
+          <t>1610212</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>182010</t>
+          <t>187890</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>160886</t>
+          <t>166121</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>205770</t>
+          <t>211276</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>243593</t>
+          <t>259673</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>195820</t>
+          <t>236279</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>273792</t>
+          <t>284570</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>425603</t>
+          <t>447563</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>377911</t>
+          <t>416347</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>460379</t>
+          <t>478384</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>743805</t>
+          <t>801193</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>720045</t>
+          <t>777807</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>764929</t>
+          <t>822962</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>847304</t>
+          <t>856885</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>817105</t>
+          <t>831988</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>895077</t>
+          <t>880279</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1591108</t>
+          <t>1658079</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1556332</t>
+          <t>1627258</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1638800</t>
+          <t>1689295</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>80,23%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>925815</t>
+          <t>989083</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>925815</t>
+          <t>989083</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>925815</t>
+          <t>989083</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1090897</t>
+          <t>1116558</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1090897</t>
+          <t>1116558</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1090897</t>
+          <t>1116558</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2016711</t>
+          <t>2105642</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2016711</t>
+          <t>2105642</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2016711</t>
+          <t>2105642</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>621253</t>
+          <t>675270</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>483909</t>
+          <t>632575</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>689114</t>
+          <t>724668</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>919978</t>
+          <t>781108</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>742025</t>
+          <t>740525</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1477015</t>
+          <t>822721</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1541231</t>
+          <t>1456378</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1335900</t>
+          <t>1398603</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2124866</t>
+          <t>1516704</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2834312</t>
+          <t>2851727</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2766451</t>
+          <t>2802329</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2971656</t>
+          <t>2894422</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2735218</t>
+          <t>2948152</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2178181</t>
+          <t>2906539</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2913171</t>
+          <t>2988735</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5569530</t>
+          <t>5799878</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4985895</t>
+          <t>5739552</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5774861</t>
+          <t>5857653</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>80,73%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3455565</t>
+          <t>3526997</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3455565</t>
+          <t>3526997</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3455565</t>
+          <t>3526997</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3655196</t>
+          <t>3729260</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3655196</t>
+          <t>3729260</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3655196</t>
+          <t>3729260</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7110761</t>
+          <t>7256256</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7110761</t>
+          <t>7256256</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7110761</t>
+          <t>7256256</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
